--- a/K9HZ_LPF_Module/K9HZ_LPF_BOMs/K9HZ_100W_LPF-Filter_Board_BOM_V1.00_09-22-24.xlsx
+++ b/K9HZ_LPF_Module/K9HZ_LPF_BOMs/K9HZ_100W_LPF-Filter_Board_BOM_V1.00_09-22-24.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dad\Documents\GitHub\K9HZ\K9HZ_LPF_Module\K9HZ_LPF_V1.00_BOMs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bill\Documents\GitHub\K9HZ\K9HZ_LPF_Module\K9HZ_LPF_BOMs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFC6E8F2-6547-4B5C-82FA-217A3046EFB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2393D0D-3679-45BE-AEED-6139CE776A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="K9HZ-11-Band-LPF-100W" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="153">
   <si>
     <t>Qty</t>
   </si>
@@ -486,6 +486,12 @@
   </si>
   <si>
     <t>80-C1206C560J2G</t>
+  </si>
+  <si>
+    <t>8 Turns of #20 Wire on a T68-6 Core.</t>
+  </si>
+  <si>
+    <t>(originally was 7 turns in error)</t>
   </si>
 </sst>
 </file>
@@ -1361,19 +1367,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H54"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.81640625" style="5"/>
-    <col min="2" max="2" width="24.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="53.08984375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="22.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.36328125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" style="5"/>
+    <col min="2" max="2" width="24.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="53.109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="22.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.77734375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1396,7 +1402,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1410,7 +1416,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="5">
         <v>5</v>
       </c>
@@ -1424,7 +1430,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="5">
         <v>4</v>
       </c>
@@ -1438,7 +1444,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="5">
         <v>1</v>
       </c>
@@ -1452,7 +1458,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="5">
         <v>3</v>
       </c>
@@ -1466,7 +1472,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="5">
         <v>2</v>
       </c>
@@ -1480,7 +1486,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>124</v>
       </c>
@@ -1497,7 +1503,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="5">
         <v>2</v>
       </c>
@@ -1511,7 +1517,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="5">
         <v>8</v>
       </c>
@@ -1525,7 +1531,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="5">
         <v>2</v>
       </c>
@@ -1539,7 +1545,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="5">
         <v>9</v>
       </c>
@@ -1553,7 +1559,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="5">
         <v>2</v>
       </c>
@@ -1567,7 +1573,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="5">
         <v>11</v>
       </c>
@@ -1581,7 +1587,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="5">
         <v>2</v>
       </c>
@@ -1595,7 +1601,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="5">
         <v>4</v>
       </c>
@@ -1609,7 +1615,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>13</v>
       </c>
@@ -1623,7 +1629,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="5">
         <v>2</v>
       </c>
@@ -1637,7 +1643,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="5">
         <v>6</v>
       </c>
@@ -1651,7 +1657,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="5">
         <v>2</v>
       </c>
@@ -1665,7 +1671,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="5">
         <v>2</v>
       </c>
@@ -1679,7 +1685,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="5">
         <v>2</v>
       </c>
@@ -1693,7 +1699,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="5">
         <v>2</v>
       </c>
@@ -1707,7 +1713,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A25" s="5">
         <v>24</v>
       </c>
@@ -1721,7 +1727,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="5">
         <v>2</v>
       </c>
@@ -1735,7 +1741,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="5">
         <v>1</v>
       </c>
@@ -1749,7 +1755,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A28" s="5">
         <v>24</v>
       </c>
@@ -1763,7 +1769,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="5">
         <v>1</v>
       </c>
@@ -1777,7 +1783,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="5">
         <v>2</v>
       </c>
@@ -1791,7 +1797,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="5">
         <v>1</v>
       </c>
@@ -1805,7 +1811,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="5">
         <v>2</v>
       </c>
@@ -1819,7 +1825,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" s="5">
         <v>2</v>
       </c>
@@ -1833,7 +1839,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" s="5">
         <v>1</v>
       </c>
@@ -1847,7 +1853,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" s="5">
         <v>1</v>
       </c>
@@ -1858,10 +1864,13 @@
         <v>93</v>
       </c>
       <c r="G35" s="7" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+        <v>151</v>
+      </c>
+      <c r="H35" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" s="5">
         <v>2</v>
       </c>
@@ -1875,7 +1884,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" s="5">
         <v>1</v>
       </c>
@@ -1889,7 +1898,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" s="5">
         <v>2</v>
       </c>
@@ -1903,7 +1912,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" s="5">
         <v>1</v>
       </c>
@@ -1917,7 +1926,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" s="5">
         <v>2</v>
       </c>
@@ -1931,7 +1940,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" s="5">
         <v>1</v>
       </c>
@@ -1945,7 +1954,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" s="5">
         <v>2</v>
       </c>
@@ -1959,7 +1968,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" s="5">
         <v>1</v>
       </c>
@@ -1973,7 +1982,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" s="5">
         <v>2</v>
       </c>
@@ -1987,7 +1996,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" s="5">
         <v>1</v>
       </c>
@@ -2001,7 +2010,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" s="5">
         <v>2</v>
       </c>
@@ -2015,7 +2024,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" s="5">
         <v>1</v>
       </c>
@@ -2029,7 +2038,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" s="5">
         <v>2</v>
       </c>
@@ -2043,7 +2052,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="5">
         <v>1</v>
       </c>
@@ -2057,7 +2066,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="5">
         <v>2</v>
       </c>
@@ -2071,7 +2080,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="5">
         <f>A29+A30</f>
         <v>3</v>
@@ -2089,7 +2098,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="5">
         <f>SUM(A31:A44)</f>
         <v>21</v>
@@ -2104,7 +2113,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="5">
         <f>A45+A46+A47+A48+A49+A50</f>
         <v>9</v>
@@ -2119,7 +2128,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="5">
         <v>38</v>
       </c>

--- a/K9HZ_LPF_Module/K9HZ_LPF_BOMs/K9HZ_100W_LPF-Filter_Board_BOM_V1.00_09-22-24.xlsx
+++ b/K9HZ_LPF_Module/K9HZ_LPF_BOMs/K9HZ_100W_LPF-Filter_Board_BOM_V1.00_09-22-24.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bill\Documents\GitHub\K9HZ\K9HZ_LPF_Module\K9HZ_LPF_BOMs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2393D0D-3679-45BE-AEED-6139CE776A08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{125051F2-A426-48DE-8803-9F9E5689CB86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1615,7 +1615,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" ht="15.6" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="5">
         <v>13</v>
       </c>
